--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3015</t>
+          <t xml:space="preserve">  3015.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3015</t>
+          <t xml:space="preserve">  3015.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248</t>
+          <t xml:space="preserve"> 15248.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248</t>
+          <t xml:space="preserve"> 15248.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7008</t>
+          <t xml:space="preserve">  7008.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7008</t>
+          <t xml:space="preserve">  7008.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137420</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>137420</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165</t>
+          <t xml:space="preserve">  6165.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165</t>
+          <t xml:space="preserve">  6165.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>584710</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>584710</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>421820</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>421820</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nucleus subthalamicus Luysi</t>
+          <t>Nucleus dentatus cerebelli</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1435,94 +1435,94 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   792.82</t>
+          <t xml:space="preserve">  1232.30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008.7</t>
+          <t xml:space="preserve">  1504.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1283.3</t>
+          <t xml:space="preserve">  1836.7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.6904534560</t>
+          <t>-0.0560873352</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.15072817</t>
+          <t>-0.28930038</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.7363260</t>
+          <t>-0.5740133</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.100</t>
+          <t xml:space="preserve"> 0.894</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   336.26</t>
+          <t xml:space="preserve">  1252.00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   705.31</t>
+          <t xml:space="preserve">  1588.80</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1479.4</t>
+          <t xml:space="preserve">  2016.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.283019487</t>
+          <t>-0.072892478</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-0.5038587</t>
+          <t>-0.3615290</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-2.1543271</t>
+          <t>-0.7278165</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pallidum</t>
+          <t>Nucleus subthalamicus Luysi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1532,182 +1532,279 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15683.00</t>
+          <t xml:space="preserve">   792.82</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 19334.0</t>
+          <t xml:space="preserve">  1008.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23835.0</t>
+          <t xml:space="preserve">  1283.3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.3290429385</t>
+          <t>-0.6904534560</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.10405172</t>
+          <t>-1.15072817</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.0594843</t>
+          <t>-1.7363260</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.060</t>
+          <t xml:space="preserve"> 1.100</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15859.00</t>
+          <t xml:space="preserve">   336.26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18304.00</t>
+          <t xml:space="preserve">   705.31</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 21125.0</t>
+          <t xml:space="preserve">  1479.4</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-2.366453984</t>
+          <t xml:space="preserve"> 0.283019487</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-2.8853119</t>
+          <t>-0.5038587</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-3.4841392</t>
+          <t>-2.1543271</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>25.2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Pallidum</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 15683.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 19334.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 23835.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4711.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-2.3290429385</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-3.10405172</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-4.0594843</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1.060</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 15859.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 18304.00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 21125.0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4711.0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-2.366453984</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>-2.8853119</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-3.4841392</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Striatum</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 39986.00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 47086.0</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 55446.0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 28689</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 28689.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>-0.3937613163</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>-0.64124464</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>-0.9326724</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 0.872</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 44604.00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 54374.00</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 66284.0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 28689</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 28689.0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>-0.554741390</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>-0.8952951</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>-1.3104445</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>

--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -1107,17 +1107,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.235718234</t>
+          <t>-0.235715715</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-1.3397968</t>
+          <t>-1.3397983</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-3.4303377</t>
+          <t>-3.4303526</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">

--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -465,17 +465,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2802.80</t>
+          <t xml:space="preserve">  3455.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3513.9</t>
+          <t xml:space="preserve">   4776.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4405.4</t>
+          <t xml:space="preserve">   6602.3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,37 +485,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.0703738023</t>
+          <t>-0.1459213</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.16548186</t>
+          <t>-0.5840967</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.4611765</t>
+          <t>-1.1898208</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.452</t>
+          <t>-1.3900</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2657.10</t>
+          <t xml:space="preserve">         1832.30</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3478.30</t>
+          <t xml:space="preserve">          2294.80</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4553.4</t>
+          <t xml:space="preserve">          2874.2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.118711740</t>
+          <t xml:space="preserve">         0.39227576</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.1536752</t>
+          <t xml:space="preserve">          0.2388573</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.5102510</t>
+          <t xml:space="preserve">          0.04670867</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -562,82 +562,82 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16954.00</t>
+          <t xml:space="preserve"> 32388.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 22300.0</t>
+          <t xml:space="preserve">  40854.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 29332.0</t>
+          <t xml:space="preserve">  51532.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248.0</t>
+          <t xml:space="preserve"> 14787.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.1119277934</t>
+          <t>-1.1903017</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.46255856</t>
+          <t>-1.7628060</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.9237558</t>
+          <t>-2.4849522</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.832</t>
+          <t xml:space="preserve"> 1.0500</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16475.00</t>
+          <t xml:space="preserve">        34804.00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 22467.00</t>
+          <t xml:space="preserve">         41906.00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 30638.0</t>
+          <t xml:space="preserve">         50457.0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248.0</t>
+          <t xml:space="preserve"> 14787.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.080516143</t>
+          <t xml:space="preserve">        -1.35368596</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.4734921</t>
+          <t xml:space="preserve">         -1.8339608</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-1.0093906</t>
+          <t xml:space="preserve">         -2.41223670</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>36</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11742.00</t>
+          <t xml:space="preserve">  9483.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14419.0</t>
+          <t xml:space="preserve">  11738.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17707.0</t>
+          <t xml:space="preserve">  14528.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,37 +679,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.6755331198</t>
+          <t>-0.3531626</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.05757052</t>
+          <t>-0.6748978</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.5267161</t>
+          <t>-1.0731306</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.020</t>
+          <t xml:space="preserve"> 1.0900</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11530.00</t>
+          <t xml:space="preserve">        10277.00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13966.00</t>
+          <t xml:space="preserve">         11246.00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16918.0</t>
+          <t xml:space="preserve">         12305.0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.645199534</t>
+          <t xml:space="preserve">        -0.46652642</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.9929281</t>
+          <t xml:space="preserve">         -0.6047065</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-1.4141524</t>
+          <t xml:space="preserve">         -0.75590627</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -756,82 +756,82 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>120220.00</t>
+          <t>164150.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>142900.0</t>
+          <t xml:space="preserve"> 194490.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>169860.0</t>
+          <t xml:space="preserve"> 230440.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137420.0</t>
+          <t>137020.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1252064323</t>
+          <t>-0.1980157</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.03984397</t>
+          <t>-0.4194733</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.2360350</t>
+          <t>-0.6818683</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.947</t>
+          <t xml:space="preserve"> 0.9820</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>129170.00</t>
+          <t xml:space="preserve">       163130.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>156550.00</t>
+          <t xml:space="preserve">        194410.00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>189730.0</t>
+          <t xml:space="preserve">        231690.0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>137420.0</t>
+          <t>137020.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.060067091</t>
+          <t xml:space="preserve">        -0.19058975</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.1391649</t>
+          <t xml:space="preserve">         -0.4188846</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-0.3806269</t>
+          <t xml:space="preserve">         -0.69095474</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   787.48</t>
+          <t xml:space="preserve">   831.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1002.8</t>
+          <t xml:space="preserve">   1109.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1276.9</t>
+          <t xml:space="preserve">   1480.3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.3506868978</t>
+          <t>-1.4823134</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.99331927</t>
+          <t>-2.3119228</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.8116349</t>
+          <t>-3.4187945</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.983</t>
+          <t xml:space="preserve"> 0.8080</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   763.40</t>
+          <t xml:space="preserve">          723.26</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   979.88</t>
+          <t xml:space="preserve">          1017.90</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1257.7</t>
+          <t xml:space="preserve">          1432.6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -913,22 +913,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-1.278797986</t>
+          <t xml:space="preserve">        -1.15899021</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-1.9250102</t>
+          <t xml:space="preserve">         -2.0385154</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.7544725</t>
+          <t xml:space="preserve">         -3.27633991</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>42</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8960.20</t>
+          <t xml:space="preserve"> 21415.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12374.0</t>
+          <t xml:space="preserve">  30459.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17090.0</t>
+          <t xml:space="preserve">  43324.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -970,37 +970,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1289755058</t>
+          <t>-1.0817361</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.20292249</t>
+          <t>-1.9609526</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.6612880</t>
+          <t>-3.2115041</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.962</t>
+          <t xml:space="preserve"> 0.8490</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9089.40</t>
+          <t xml:space="preserve">        16476.00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12931.00</t>
+          <t xml:space="preserve">         25545.00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18395.0</t>
+          <t xml:space="preserve">         39607.0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1010,22 +1010,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.116421650</t>
+          <t xml:space="preserve">        -0.60164717</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.2569884</t>
+          <t xml:space="preserve">         -1.4832726</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.7882057</t>
+          <t xml:space="preserve">         -2.85018811</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1047,82 +1047,82 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1894.30</t>
+          <t xml:space="preserve">  4822.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3124.2</t>
+          <t xml:space="preserve">   8423.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5152.7</t>
+          <t xml:space="preserve">  14716.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165.0</t>
+          <t xml:space="preserve">  6479.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.6927377095</t>
+          <t xml:space="preserve"> 0.2557317</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.49323782</t>
+          <t>-0.3001777</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1642062</t>
+          <t>-1.2713073</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.117</t>
+          <t>-0.0983</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7618.20</t>
+          <t>5459800000000.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14425.00</t>
+          <t>10827000000000.00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 27313.0</t>
+          <t>21469000000000.0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165.0</t>
+          <t xml:space="preserve">  6479.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.235715715</t>
+          <t>-842684063.70056820</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-1.3397983</t>
+          <t>-1671027096.9435966</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-3.4303526</t>
+          <t>-3313616191.62849188</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8093.10</t>
+          <t xml:space="preserve"> 14336.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9097.8</t>
+          <t xml:space="preserve">  16581.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10227.0</t>
+          <t xml:space="preserve">  19179.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1164,37 +1164,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0007600654</t>
+          <t>-0.7726979</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.12498635</t>
+          <t>-1.0503860</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.2646331</t>
+          <t>-1.3715732</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.000</t>
+          <t xml:space="preserve"> 0.9950</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8073.20</t>
+          <t xml:space="preserve">        14227.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9067.80</t>
+          <t xml:space="preserve">         16493.00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10185.0</t>
+          <t xml:space="preserve">         19120.0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,22 +1204,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.001708267</t>
+          <t xml:space="preserve">        -0.75927271</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.1212809</t>
+          <t xml:space="preserve">         -1.0394476</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.2594223</t>
+          <t xml:space="preserve">         -1.36424214</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>323010.00</t>
+          <t>493470.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>411870.0</t>
+          <t xml:space="preserve"> 644120.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>525170.0</t>
+          <t xml:space="preserve"> 840760.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1261,37 +1261,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4475645369</t>
+          <t xml:space="preserve"> 0.1560388</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.29559820</t>
+          <t>-0.1016112</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1018283</t>
+          <t>-0.4379182</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.497</t>
+          <t xml:space="preserve"> 0.4230</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>330740.00</t>
+          <t xml:space="preserve">       617130.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>472550.00</t>
+          <t xml:space="preserve">        929330.00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>675160.0</t>
+          <t xml:space="preserve">       1399500.0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.434343573</t>
+          <t xml:space="preserve">        -0.05545023</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1918125</t>
+          <t xml:space="preserve">         -0.5894022</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.1547062</t>
+          <t xml:space="preserve">         -1.39348040</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>409800.00</t>
+          <t>810220.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>542610.0</t>
+          <t>1054000.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>718450.0</t>
+          <t>1371100.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1358,37 +1358,37 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.0284851483</t>
+          <t>-0.9207741</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.28635471</t>
+          <t>-1.4986844</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.7032251</t>
+          <t>-2.2504727</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.652</t>
+          <t xml:space="preserve"> 0.6530</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>386360.00</t>
+          <t xml:space="preserve">       907490.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>581630.00</t>
+          <t xml:space="preserve">       1344100.00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>875590.0</t>
+          <t xml:space="preserve">       1990900.0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1398,22 +1398,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.084069201</t>
+          <t xml:space="preserve">        -1.15136224</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-0.3788544</t>
+          <t xml:space="preserve">         -2.1865074</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-1.0757457</t>
+          <t xml:space="preserve">         -3.71972091</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1232.30</t>
+          <t xml:space="preserve">  2335.60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1504.5</t>
+          <t xml:space="preserve">   2970.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1836.7</t>
+          <t xml:space="preserve">   3778.2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1455,37 +1455,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.0560873352</t>
+          <t>-1.0015226</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.28930038</t>
+          <t>-1.5456908</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.5740133</t>
+          <t>-2.2378059</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.894</t>
+          <t xml:space="preserve"> 0.7960</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1252.00</t>
+          <t xml:space="preserve">         2134.30</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1588.80</t>
+          <t xml:space="preserve">          2903.90</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2016.2</t>
+          <t xml:space="preserve">          3951.0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1495,22 +1495,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-0.072892478</t>
+          <t xml:space="preserve">        -0.82903461</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-0.3615290</t>
+          <t xml:space="preserve">         -1.4885461</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-0.7278165</t>
+          <t xml:space="preserve">         -2.38586368</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   792.82</t>
+          <t xml:space="preserve">   629.90</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008.7</t>
+          <t xml:space="preserve">    811.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1283.3</t>
+          <t xml:space="preserve">   1044.2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1552,37 +1552,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.6904534560</t>
+          <t>-0.3430646</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.15072817</t>
+          <t>-0.7292074</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.7363260</t>
+          <t>-1.2263696</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.100</t>
+          <t xml:space="preserve"> 1.1100</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   336.26</t>
+          <t xml:space="preserve">          365.42</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   705.31</t>
+          <t xml:space="preserve">           746.47</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1479.4</t>
+          <t xml:space="preserve">          1524.9</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1592,22 +1592,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.283019487</t>
+          <t xml:space="preserve">         0.22086320</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.5038587</t>
+          <t xml:space="preserve">         -0.5916202</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-2.1543271</t>
+          <t xml:space="preserve">         -2.25136092</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15683.00</t>
+          <t xml:space="preserve">  9472.70</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 19334.0</t>
+          <t xml:space="preserve">  11831.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23835.0</t>
+          <t xml:space="preserve">  14776.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1649,37 +1649,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.3290429385</t>
+          <t>-1.0107644</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.10405172</t>
+          <t>-1.5113271</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.0594843</t>
+          <t>-2.1365008</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.060</t>
+          <t xml:space="preserve"> 0.9700</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15859.00</t>
+          <t xml:space="preserve">         9314.20</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18304.00</t>
+          <t xml:space="preserve">         11878.00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 21125.0</t>
+          <t xml:space="preserve">         15147.0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-2.366453984</t>
+          <t xml:space="preserve">        -0.97711771</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-2.8853119</t>
+          <t xml:space="preserve">         -1.5212788</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-3.4841392</t>
+          <t xml:space="preserve">         -2.21520910</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 39986.00</t>
+          <t xml:space="preserve"> 73442.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 47086.0</t>
+          <t xml:space="preserve">  90742.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 55446.0</t>
+          <t xml:space="preserve"> 112120.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1746,37 +1746,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.3937613163</t>
+          <t>-1.5599226</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.64124464</t>
+          <t>-2.1629377</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.9326724</t>
+          <t>-2.9079990</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.872</t>
+          <t xml:space="preserve"> 0.5540</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 44604.00</t>
+          <t xml:space="preserve">        63680.00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 54374.00</t>
+          <t xml:space="preserve">         84042.00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 66284.0</t>
+          <t xml:space="preserve">        110920.0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-0.554741390</t>
+          <t xml:space="preserve">        -1.21965486</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-0.8952951</t>
+          <t xml:space="preserve">         -1.9294280</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-1.3104445</t>
+          <t xml:space="preserve">         -2.86616354</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">

--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -465,17 +465,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3455.00</t>
+          <t xml:space="preserve">  3529.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4776.1</t>
+          <t xml:space="preserve">  4731.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6602.3</t>
+          <t xml:space="preserve">   6341.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,37 +485,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.1459213</t>
+          <t>-0.17065794</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.5840967</t>
+          <t>-0.56914161</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.1898208</t>
+          <t>-1.1032663</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.3900</t>
+          <t xml:space="preserve"> 0.3260</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">         1832.30</t>
+          <t xml:space="preserve">  3580.10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">          2294.80</t>
+          <t xml:space="preserve">  4720.30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">          2874.2</t>
+          <t xml:space="preserve">   6223.60</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">         0.39227576</t>
+          <t>-0.18741498</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">          0.2388573</t>
+          <t>-0.565595329</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">          0.04670867</t>
+          <t>-1.0642225</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32388.00</t>
+          <t xml:space="preserve"> 12567.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  40854.0</t>
+          <t xml:space="preserve"> 15682.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  51532.0</t>
+          <t xml:space="preserve">  19570.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -582,17 +582,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.1903017</t>
+          <t xml:space="preserve"> 0.15015021</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.7628060</t>
+          <t>-0.06054501</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.4849522</t>
+          <t>-0.3234759</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        34804.00</t>
+          <t xml:space="preserve"> 11561.00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         41906.00</t>
+          <t xml:space="preserve"> 13851.00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         50457.0</t>
+          <t xml:space="preserve">  16595.00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -1.35368596</t>
+          <t xml:space="preserve"> 0.21819401</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.8339608</t>
+          <t xml:space="preserve"> 0.063296770</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.41223670</t>
+          <t>-0.1222899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9483.00</t>
+          <t xml:space="preserve">  7296.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11738.0</t>
+          <t xml:space="preserve">  8975.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14528.0</t>
+          <t xml:space="preserve">  11040.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,37 +679,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.3531626</t>
+          <t>-0.04123024</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.6748978</t>
+          <t>-0.28076806</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0731306</t>
+          <t>-0.5754122</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0900</t>
+          <t xml:space="preserve"> 1.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        10277.00</t>
+          <t xml:space="preserve">  7296.80</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">         11246.00</t>
+          <t xml:space="preserve">  8977.10</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">         12305.0</t>
+          <t xml:space="preserve">  11044.00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.46652642</t>
+          <t>-0.04120498</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.6047065</t>
+          <t>-0.280979606</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.75590627</t>
+          <t>-0.5759709</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -756,82 +756,82 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>164150.00</t>
+          <t xml:space="preserve"> 54422.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 194490.0</t>
+          <t xml:space="preserve"> 64137.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 230440.0</t>
+          <t xml:space="preserve">  75585.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137020.0</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.1980157</t>
+          <t xml:space="preserve"> 0.60397463</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.4194733</t>
+          <t xml:space="preserve"> 0.53328343</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.6818683</t>
+          <t xml:space="preserve"> 0.4499737</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9820</t>
+          <t xml:space="preserve"> 0.9950</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">       163130.00</t>
+          <t xml:space="preserve"> 55003.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        194410.00</t>
+          <t xml:space="preserve"> 64966.00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        231690.0</t>
+          <t xml:space="preserve">  76733.00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>137020.0</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.19058975</t>
+          <t xml:space="preserve"> 0.59974671</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.4188846</t>
+          <t xml:space="preserve"> 0.527250664</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.69095474</t>
+          <t xml:space="preserve"> 0.4416237</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   831.57</t>
+          <t xml:space="preserve">   492.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1109.5</t>
+          <t xml:space="preserve">   637.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1480.3</t>
+          <t xml:space="preserve">    826.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.4823134</t>
+          <t>-0.46915350</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.3119228</t>
+          <t>-0.90358722</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.4187945</t>
+          <t>-1.4664845</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.8080</t>
+          <t xml:space="preserve"> 0.8800</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">          723.26</t>
+          <t xml:space="preserve">   462.29</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1017.90</t>
+          <t xml:space="preserve">   622.56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1432.6</t>
+          <t xml:space="preserve">    838.41</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -913,22 +913,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -1.15899021</t>
+          <t>-0.37995642</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.0385154</t>
+          <t>-0.858401342</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -3.27633991</t>
+          <t>-1.5027280</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 21415.00</t>
+          <t xml:space="preserve">  4261.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  30459.0</t>
+          <t xml:space="preserve">  5799.40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  43324.0</t>
+          <t xml:space="preserve">   7892.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -970,37 +970,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.0817361</t>
+          <t xml:space="preserve"> 0.58575336</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.9609526</t>
+          <t xml:space="preserve"> 0.43624312</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.2115041</t>
+          <t xml:space="preserve"> 0.2327715</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.8490</t>
+          <t xml:space="preserve"> 0.9470</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        16476.00</t>
+          <t xml:space="preserve">  4405.30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">         25545.00</t>
+          <t xml:space="preserve">  6224.30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">         39607.0</t>
+          <t xml:space="preserve">   8794.40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1010,22 +1010,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.60164717</t>
+          <t xml:space="preserve"> 0.57175689</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.4832726</t>
+          <t xml:space="preserve"> 0.394931234</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.85018811</t>
+          <t xml:space="preserve"> 0.1450926</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4822.10</t>
+          <t xml:space="preserve">  5517.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8423.9</t>
+          <t xml:space="preserve">  9297.70</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14716.0</t>
+          <t xml:space="preserve">  15668.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1067,37 +1067,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2557317</t>
+          <t xml:space="preserve"> 0.14843407</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.3001777</t>
+          <t>-0.43504505</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.2713073</t>
+          <t>-1.4183146</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0983</t>
+          <t>-0.0996</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5459800000000.00</t>
+          <t xml:space="preserve">   857.29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10827000000000.00</t>
+          <t xml:space="preserve">  2219.10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>21469000000000.0</t>
+          <t xml:space="preserve">   5744.30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1107,22 +1107,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-842684063.70056820</t>
+          <t xml:space="preserve"> 0.86768163</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-1671027096.9435966</t>
+          <t xml:space="preserve"> 0.657487921</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-3313616191.62849188</t>
+          <t xml:space="preserve"> 0.1133920</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14336.00</t>
+          <t xml:space="preserve">  4757.70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16581.0</t>
+          <t xml:space="preserve">  5350.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19179.0</t>
+          <t xml:space="preserve">   6018.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1164,37 +1164,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.7726979</t>
+          <t xml:space="preserve"> 0.41169014</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.0503860</t>
+          <t xml:space="preserve"> 0.33834046</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.3715732</t>
+          <t xml:space="preserve"> 0.2558456</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9950</t>
+          <t xml:space="preserve"> 1.0000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">        14227.00</t>
+          <t xml:space="preserve">  4733.50</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         16493.00</t>
+          <t xml:space="preserve">  5314.90</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         19120.0</t>
+          <t xml:space="preserve">   5967.90</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,22 +1204,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.75927271</t>
+          <t xml:space="preserve"> 0.41468363</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.0394476</t>
+          <t xml:space="preserve"> 0.342778738</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.36424214</t>
+          <t xml:space="preserve"> 0.2620405</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>493470.00</t>
+          <t>541780.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 644120.0</t>
+          <t>668170.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 840760.0</t>
+          <t xml:space="preserve"> 824050.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1261,37 +1261,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1560388</t>
+          <t xml:space="preserve"> 0.07341585</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.1016112</t>
+          <t>-0.14274601</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.4379182</t>
+          <t>-0.4093360</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4230</t>
+          <t xml:space="preserve"> 0.5910</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">       617130.00</t>
+          <t>672350.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">        929330.00</t>
+          <t>918910.00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">       1399500.0</t>
+          <t>1255900.00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.05545023</t>
+          <t>-0.14989128</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.5894022</t>
+          <t>-0.571571058</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.39348040</t>
+          <t>-1.1478862</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>810220.00</t>
+          <t>702360.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1054000.0</t>
+          <t>883370.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1371100.0</t>
+          <t>1111000.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1358,37 +1358,37 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.9207741</t>
+          <t>-0.66508386</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.4986844</t>
+          <t>-1.09419663</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.2504727</t>
+          <t>-1.6338971</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.6530</t>
+          <t xml:space="preserve"> 1.0700</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       907490.00</t>
+          <t>718050.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       1344100.00</t>
+          <t>819010.00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">       1990900.0</t>
+          <t xml:space="preserve"> 934170.00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1398,22 +1398,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -1.15136224</t>
+          <t>-0.70226622</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.1865074</t>
+          <t>-0.941615765</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -3.71972091</t>
+          <t>-1.2146194</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2335.60</t>
+          <t xml:space="preserve">   498.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2970.6</t>
+          <t xml:space="preserve">   602.93</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3778.2</t>
+          <t xml:space="preserve">    729.68</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1455,37 +1455,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.0015226</t>
+          <t xml:space="preserve"> 0.57306277</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.5456908</t>
+          <t xml:space="preserve"> 0.48330665</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.2378059</t>
+          <t xml:space="preserve"> 0.3746809</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.7960</t>
+          <t xml:space="preserve"> 0.9470</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">         2134.30</t>
+          <t xml:space="preserve">   555.80</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">          2903.90</t>
+          <t xml:space="preserve">   688.06</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">          3951.0</t>
+          <t xml:space="preserve">    851.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1495,22 +1495,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.82903461</t>
+          <t xml:space="preserve"> 0.52369514</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.4885461</t>
+          <t xml:space="preserve"> 0.410352865</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.38586368</t>
+          <t xml:space="preserve"> 0.2700395</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   629.90</t>
+          <t xml:space="preserve">   512.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    811.0</t>
+          <t xml:space="preserve">   649.73</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1044.2</t>
+          <t xml:space="preserve">    824.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.3430646</t>
+          <t>-0.09207099</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.7292074</t>
+          <t>-0.38535844</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.2263696</t>
+          <t>-0.7574114</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">          365.42</t>
+          <t xml:space="preserve">   390.18</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">           746.47</t>
+          <t xml:space="preserve">   826.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1524.9</t>
+          <t xml:space="preserve">   1748.70</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1592,22 +1592,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">         0.22086320</t>
+          <t xml:space="preserve"> 0.16806569</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -0.5916202</t>
+          <t>-0.761239458</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.25136092</t>
+          <t>-2.7286170</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9472.70</t>
+          <t xml:space="preserve">  7687.50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11831.0</t>
+          <t xml:space="preserve">  9422.20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  14776.0</t>
+          <t xml:space="preserve">  11548.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1649,37 +1649,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.0107644</t>
+          <t>-0.63181293</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.5113271</t>
+          <t>-1.00003442</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.1365008</t>
+          <t>-1.4513457</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9700</t>
+          <t xml:space="preserve"> 1.0500</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         9314.20</t>
+          <t xml:space="preserve">  8058.40</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         11878.00</t>
+          <t xml:space="preserve">  9462.60</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         15147.0</t>
+          <t xml:space="preserve">  11111.00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -0.97711771</t>
+          <t>-0.71055282</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.5212788</t>
+          <t>-1.008609255</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.21520910</t>
+          <t>-1.3586007</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 73442.00</t>
+          <t xml:space="preserve"> 14860.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  90742.0</t>
+          <t xml:space="preserve"> 17710.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 112120.0</t>
+          <t xml:space="preserve">  21107.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1746,37 +1746,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.5599226</t>
+          <t xml:space="preserve"> 0.48202309</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.1629377</t>
+          <t xml:space="preserve"> 0.38267503</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.9079990</t>
+          <t xml:space="preserve"> 0.2642720</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.5540</t>
+          <t xml:space="preserve"> 0.7500</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        63680.00</t>
+          <t xml:space="preserve"> 23015.00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">         84042.00</t>
+          <t xml:space="preserve"> 28816.00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        110920.0</t>
+          <t xml:space="preserve">  36078.00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        -1.21965486</t>
+          <t xml:space="preserve"> 0.19778175</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -1.9294280</t>
+          <t>-0.004413484</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">         -2.86616354</t>
+          <t>-0.2575710</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">

--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,17 +465,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3529.50</t>
+          <t xml:space="preserve">  2802.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4731.00</t>
+          <t xml:space="preserve">  3513.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6341.30</t>
+          <t xml:space="preserve">  4405.4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,37 +485,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.17065794</t>
+          <t xml:space="preserve"> 0.0703738023</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.56914161</t>
+          <t>-0.1654819</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.1032663</t>
+          <t>-0.4611765</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.3260</t>
+          <t xml:space="preserve"> 0.452</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3580.10</t>
+          <t xml:space="preserve">  2657.10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4720.30</t>
+          <t xml:space="preserve">  3478.30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6223.60</t>
+          <t xml:space="preserve">  4553.4</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.18741498</t>
+          <t xml:space="preserve"> 0.118711740</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.565595329</t>
+          <t>-0.1536752</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.0642225</t>
+          <t>-0.5102510</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -562,82 +562,82 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12567.00</t>
+          <t xml:space="preserve"> 16954.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15682.00</t>
+          <t xml:space="preserve"> 22300.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19570.00</t>
+          <t xml:space="preserve"> 29332.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14787.0</t>
+          <t xml:space="preserve"> 15248.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.15015021</t>
+          <t>-0.1119277934</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.06054501</t>
+          <t>-0.4625586</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3234759</t>
+          <t>-0.9237558</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0500</t>
+          <t xml:space="preserve"> 0.832</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11561.00</t>
+          <t xml:space="preserve"> 16475.00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13851.00</t>
+          <t xml:space="preserve"> 22467.00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  16595.00</t>
+          <t xml:space="preserve"> 30638.0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14787.0</t>
+          <t xml:space="preserve"> 15248.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.21819401</t>
+          <t>-0.080516143</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.063296770</t>
+          <t>-0.4734921</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.1222899</t>
+          <t>-1.0093906</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7296.90</t>
+          <t xml:space="preserve"> 11742.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8975.60</t>
+          <t xml:space="preserve"> 14419.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11040.00</t>
+          <t xml:space="preserve"> 17707.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,37 +679,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.04123024</t>
+          <t>-0.6755331198</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.28076806</t>
+          <t>-1.0575705</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.5754122</t>
+          <t>-1.5267161</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0000</t>
+          <t xml:space="preserve"> 1.020</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7296.80</t>
+          <t xml:space="preserve"> 11530.00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8977.10</t>
+          <t xml:space="preserve"> 13966.00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11044.00</t>
+          <t xml:space="preserve"> 16918.0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.04120498</t>
+          <t>-0.645199534</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.280979606</t>
+          <t>-0.9929281</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.5759709</t>
+          <t>-1.4141524</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerebellum</t>
+          <t>Corpus geniculatum laterale</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -756,94 +756,94 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 54422.00</t>
+          <t xml:space="preserve">   787.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 64137.00</t>
+          <t xml:space="preserve">  1002.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  75585.00</t>
+          <t xml:space="preserve">  1276.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137420.0</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.60397463</t>
+          <t>-1.3506868978</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.53328343</t>
+          <t>-1.9933193</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4499737</t>
+          <t>-2.8116349</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9950</t>
+          <t xml:space="preserve"> 0.983</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 55003.00</t>
+          <t xml:space="preserve">   763.40</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 64966.00</t>
+          <t xml:space="preserve">   979.88</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  76733.00</t>
+          <t xml:space="preserve">  1257.7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>137420.0</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.59974671</t>
+          <t>-1.278797986</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.527250664</t>
+          <t>-1.9250102</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4416237</t>
+          <t>-2.7544725</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>23.1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corpus geniculatum laterale</t>
+          <t>Hippocampus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -853,94 +853,94 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   492.17</t>
+          <t xml:space="preserve">  8960.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   637.70</t>
+          <t xml:space="preserve"> 12374.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    826.27</t>
+          <t xml:space="preserve"> 17090.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335.0</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.46915350</t>
+          <t xml:space="preserve"> 0.1289755058</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.90358722</t>
+          <t>-0.2029225</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.4664845</t>
+          <t>-0.6612880</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.8800</t>
+          <t xml:space="preserve"> 0.962</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   462.29</t>
+          <t xml:space="preserve">  9089.40</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   622.56</t>
+          <t xml:space="preserve"> 12931.00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    838.41</t>
+          <t xml:space="preserve"> 18395.0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335.0</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.37995642</t>
+          <t xml:space="preserve"> 0.116421650</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.858401342</t>
+          <t>-0.2569884</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5027280</t>
+          <t>-0.7882057</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
+          <t>Insular cortex (grey)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -950,94 +950,94 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4261.40</t>
+          <t xml:space="preserve">  1894.30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5799.40</t>
+          <t xml:space="preserve">  3124.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7892.50</t>
+          <t xml:space="preserve">  5152.7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287.0</t>
+          <t xml:space="preserve">  6165.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.58575336</t>
+          <t xml:space="preserve"> 0.6927377095</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.43624312</t>
+          <t xml:space="preserve"> 0.4932378</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2327715</t>
+          <t xml:space="preserve"> 0.1642062</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9470</t>
+          <t>-0.117</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4405.30</t>
+          <t xml:space="preserve">  7618.20</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6224.30</t>
+          <t xml:space="preserve"> 14425.00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8794.40</t>
+          <t xml:space="preserve"> 27313.0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287.0</t>
+          <t xml:space="preserve">  6165.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.57175689</t>
+          <t>-0.235715715</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.394931234</t>
+          <t>-1.3397983</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1450926</t>
+          <t>-3.4303526</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>30.3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Insular cortex (grey)</t>
+          <t>Mesencephalon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1047,94 +1047,94 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5517.30</t>
+          <t xml:space="preserve">  8093.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9297.70</t>
+          <t xml:space="preserve">  9097.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15668.00</t>
+          <t xml:space="preserve"> 10227.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6479.0</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.14843407</t>
+          <t>-0.0007600654</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.43504505</t>
+          <t>-0.1249863</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.4183146</t>
+          <t>-0.2646331</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0996</t>
+          <t xml:space="preserve"> 1.000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   857.29</t>
+          <t xml:space="preserve">  8073.20</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2219.10</t>
+          <t xml:space="preserve">  9067.80</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5744.30</t>
+          <t xml:space="preserve"> 10185.0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6479.0</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.86768163</t>
+          <t xml:space="preserve"> 0.001708267</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.657487921</t>
+          <t>-0.1212809</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1133920</t>
+          <t>-0.2594223</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>25.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mesencephalon</t>
+          <t>Neocortex grey</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1144,94 +1144,94 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4757.70</t>
+          <t>323010.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5350.80</t>
+          <t>411870.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6018.00</t>
+          <t>525170.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087.0</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.41169014</t>
+          <t xml:space="preserve"> 0.4475645369</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.33834046</t>
+          <t xml:space="preserve"> 0.2955982</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2558456</t>
+          <t xml:space="preserve"> 0.1018283</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0000</t>
+          <t xml:space="preserve"> 0.497</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4733.50</t>
+          <t>330740.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5314.90</t>
+          <t>472550.00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5967.90</t>
+          <t>675160.0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087.0</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.41468363</t>
+          <t xml:space="preserve"> 0.434343573</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.342778738</t>
+          <t xml:space="preserve"> 0.1918125</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2620405</t>
+          <t>-0.1547062</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>33.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Neocortex grey</t>
+          <t>Neocortex white</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1241,94 +1241,94 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>541780.00</t>
+          <t>409800.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>668170.00</t>
+          <t>542610.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 824050.00</t>
+          <t>718450.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>584710.0</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.07341585</t>
+          <t xml:space="preserve"> 0.0284851483</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.14274601</t>
+          <t>-0.2863547</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.4093360</t>
+          <t>-0.7032251</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.5910</t>
+          <t xml:space="preserve"> 0.652</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>672350.00</t>
+          <t>386360.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>918910.00</t>
+          <t>581630.00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1255900.00</t>
+          <t>875590.0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>584710.0</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.14989128</t>
+          <t xml:space="preserve"> 0.084069201</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-0.571571058</t>
+          <t>-0.3788544</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-1.1478862</t>
+          <t>-1.0757457</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>12.3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neocortex white</t>
+          <t>Nucleus dentatus cerebelli</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1338,94 +1338,94 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>702360.00</t>
+          <t xml:space="preserve">  1232.30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>883370.00</t>
+          <t xml:space="preserve">  1504.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1111000.00</t>
+          <t xml:space="preserve">  1836.7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>421820.0</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.66508386</t>
+          <t>-0.0560873352</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.09419663</t>
+          <t>-0.2893004</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.6338971</t>
+          <t>-0.5740133</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0700</t>
+          <t xml:space="preserve"> 0.894</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>718050.00</t>
+          <t xml:space="preserve">  1252.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>819010.00</t>
+          <t xml:space="preserve">  1588.80</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 934170.00</t>
+          <t xml:space="preserve">  2016.2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>421820.0</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-0.70226622</t>
+          <t>-0.072892478</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-0.941615765</t>
+          <t>-0.3615290</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-1.2146194</t>
+          <t>-0.7278165</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>24.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nucleus dentatus cerebelli</t>
+          <t>Nucleus subthalamicus Luysi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1435,94 +1435,94 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   498.19</t>
+          <t xml:space="preserve">   792.82</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   602.93</t>
+          <t xml:space="preserve">  1008.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    729.68</t>
+          <t xml:space="preserve">  1283.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1166.9</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.57306277</t>
+          <t>-0.6904534560</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.48330665</t>
+          <t>-1.1507282</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.3746809</t>
+          <t>-1.7363260</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.9470</t>
+          <t xml:space="preserve"> 1.100</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   555.80</t>
+          <t xml:space="preserve">   336.26</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   688.06</t>
+          <t xml:space="preserve">   705.31</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    851.79</t>
+          <t xml:space="preserve">  1479.4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1166.9</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.52369514</t>
+          <t xml:space="preserve"> 0.283019487</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.410352865</t>
+          <t>-0.5038587</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2700395</t>
+          <t>-2.1543271</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nucleus subthalamicus Luysi</t>
+          <t>Pallidum</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1532,94 +1532,94 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   512.18</t>
+          <t xml:space="preserve"> 15683.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   649.73</t>
+          <t xml:space="preserve"> 19334.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    824.23</t>
+          <t xml:space="preserve"> 23835.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469.0</t>
+          <t xml:space="preserve">  4711.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.09207099</t>
+          <t>-2.3290429385</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.38535844</t>
+          <t>-3.1040517</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.7574114</t>
+          <t>-4.0594843</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.1100</t>
+          <t xml:space="preserve"> 1.060</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   390.18</t>
+          <t xml:space="preserve"> 15859.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   826.02</t>
+          <t xml:space="preserve"> 18304.00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1748.70</t>
+          <t xml:space="preserve"> 21125.0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469.0</t>
+          <t xml:space="preserve">  4711.0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.16806569</t>
+          <t>-2.366453984</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.761239458</t>
+          <t>-2.8853119</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-2.7286170</t>
+          <t>-3.4841392</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>21.9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pallidum</t>
+          <t>Striatum</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1629,182 +1629,85 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7687.50</t>
+          <t xml:space="preserve"> 39986.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9422.20</t>
+          <t xml:space="preserve"> 47086.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11548.00</t>
+          <t xml:space="preserve"> 55446.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711.0</t>
+          <t xml:space="preserve"> 28689.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.63181293</t>
+          <t>-0.3937613163</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.00003442</t>
+          <t>-0.6412446</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.4513457</t>
+          <t>-0.9326724</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.0500</t>
+          <t xml:space="preserve"> 0.872</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8058.40</t>
+          <t xml:space="preserve"> 44604.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9462.60</t>
+          <t xml:space="preserve"> 54374.00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11111.00</t>
+          <t xml:space="preserve"> 66284.0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711.0</t>
+          <t xml:space="preserve"> 28689.0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-0.71055282</t>
+          <t>-0.554741390</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-1.008609255</t>
+          <t>-0.8952951</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-1.3586007</t>
+          <t>-1.3104445</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Striatum</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 14860.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 17710.00</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  21107.00</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 28689.0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.48202309</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.38267503</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.2642720</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.7500</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 23015.00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 28816.00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  36078.00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 28689.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.19778175</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-0.004413484</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-0.2575710</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>

--- a/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
+++ b/tables/s3/all/Table 4 Predicted volumes for Brownian and Pagel's lambda models.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,17 +465,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2802.80</t>
+          <t xml:space="preserve">  3529.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3513.9</t>
+          <t xml:space="preserve">  4731.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4405.4</t>
+          <t xml:space="preserve">   6341.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,37 +485,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.0703738023</t>
+          <t>-0.17065794</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.1654819</t>
+          <t>-0.56914161</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.4611765</t>
+          <t>-1.1032663</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.452</t>
+          <t xml:space="preserve"> 0.3260</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2657.10</t>
+          <t xml:space="preserve">  3580.10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3478.30</t>
+          <t xml:space="preserve">  4720.30</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4553.4</t>
+          <t xml:space="preserve">   6223.60</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -525,22 +525,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.118711740</t>
+          <t>-0.18741498</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.1536752</t>
+          <t>-0.565595329</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.5102510</t>
+          <t>-1.0642225</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -562,82 +562,82 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16954.00</t>
+          <t xml:space="preserve"> 12567.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 22300.0</t>
+          <t xml:space="preserve"> 15682.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 29332.0</t>
+          <t xml:space="preserve">  19570.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248.0</t>
+          <t xml:space="preserve"> 14787.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.1119277934</t>
+          <t xml:space="preserve"> 0.15015021</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.4625586</t>
+          <t>-0.06054501</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.9237558</t>
+          <t>-0.3234759</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.832</t>
+          <t xml:space="preserve"> 1.0500</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16475.00</t>
+          <t xml:space="preserve"> 11561.00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 22467.00</t>
+          <t xml:space="preserve"> 13851.00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 30638.0</t>
+          <t xml:space="preserve">  16595.00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15248.0</t>
+          <t xml:space="preserve"> 14787.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.080516143</t>
+          <t xml:space="preserve"> 0.21819401</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.4734921</t>
+          <t xml:space="preserve"> 0.063296770</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-1.0093906</t>
+          <t>-0.1222899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11742.00</t>
+          <t xml:space="preserve">  7296.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14419.0</t>
+          <t xml:space="preserve">  8975.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17707.0</t>
+          <t xml:space="preserve">  11040.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -679,37 +679,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.6755331198</t>
+          <t>-0.04123024</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.0575705</t>
+          <t>-0.28076806</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.5267161</t>
+          <t>-0.5754122</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.020</t>
+          <t xml:space="preserve"> 1.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11530.00</t>
+          <t xml:space="preserve">  7296.80</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13966.00</t>
+          <t xml:space="preserve">  8977.10</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16918.0</t>
+          <t xml:space="preserve">  11044.00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.645199534</t>
+          <t>-0.04120498</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.9929281</t>
+          <t>-0.280979606</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-1.4141524</t>
+          <t>-0.5759709</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corpus geniculatum laterale</t>
+          <t>Cerebellum</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -756,94 +756,94 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   787.48</t>
+          <t xml:space="preserve"> 54422.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1002.8</t>
+          <t xml:space="preserve"> 64137.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1276.9</t>
+          <t xml:space="preserve">  75585.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335.0</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.3506868978</t>
+          <t xml:space="preserve"> 0.60397463</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.9933193</t>
+          <t xml:space="preserve"> 0.53328343</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.8116349</t>
+          <t xml:space="preserve"> 0.4499737</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.983</t>
+          <t xml:space="preserve"> 0.9950</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   763.40</t>
+          <t xml:space="preserve"> 55003.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   979.88</t>
+          <t xml:space="preserve"> 64966.00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1257.7</t>
+          <t xml:space="preserve">  76733.00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   335.0</t>
+          <t>137420.0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-1.278797986</t>
+          <t xml:space="preserve"> 0.59974671</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-1.9250102</t>
+          <t xml:space="preserve"> 0.527250664</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-2.7544725</t>
+          <t xml:space="preserve"> 0.4416237</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>29.8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hippocampus</t>
+          <t>Corpus geniculatum laterale</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -853,94 +853,94 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8960.20</t>
+          <t xml:space="preserve">   492.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12374.0</t>
+          <t xml:space="preserve">   637.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17090.0</t>
+          <t xml:space="preserve">    826.27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287.0</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1289755058</t>
+          <t>-0.46915350</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.2029225</t>
+          <t>-0.90358722</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.6612880</t>
+          <t>-1.4664845</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.962</t>
+          <t xml:space="preserve"> 0.8800</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9089.40</t>
+          <t xml:space="preserve">   462.29</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12931.00</t>
+          <t xml:space="preserve">   622.56</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18395.0</t>
+          <t xml:space="preserve">    838.41</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10287.0</t>
+          <t xml:space="preserve">   335.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.116421650</t>
+          <t>-0.37995642</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.2569884</t>
+          <t>-0.858401342</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.7882057</t>
+          <t>-1.5027280</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Insular cortex (grey)</t>
+          <t>Hippocampus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -950,94 +950,94 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1894.30</t>
+          <t xml:space="preserve">  4261.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3124.2</t>
+          <t xml:space="preserve">  5799.40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5152.7</t>
+          <t xml:space="preserve">   7892.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165.0</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.6927377095</t>
+          <t xml:space="preserve"> 0.58575336</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4932378</t>
+          <t xml:space="preserve"> 0.43624312</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1642062</t>
+          <t xml:space="preserve"> 0.2327715</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.117</t>
+          <t xml:space="preserve"> 0.9470</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7618.20</t>
+          <t xml:space="preserve">  4405.30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14425.00</t>
+          <t xml:space="preserve">  6224.30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 27313.0</t>
+          <t xml:space="preserve">   8794.40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6165.0</t>
+          <t xml:space="preserve"> 10287.0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.235715715</t>
+          <t xml:space="preserve"> 0.57175689</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-1.3397983</t>
+          <t xml:space="preserve"> 0.394931234</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-3.4303526</t>
+          <t xml:space="preserve"> 0.1450926</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>25.7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mesencephalon</t>
+          <t>Insular cortex (grey)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1047,94 +1047,94 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8093.10</t>
+          <t xml:space="preserve">  5517.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9097.8</t>
+          <t xml:space="preserve">  9297.70</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10227.0</t>
+          <t xml:space="preserve">  15668.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087.0</t>
+          <t xml:space="preserve">  6479.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.0007600654</t>
+          <t xml:space="preserve"> 0.14843407</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.1249863</t>
+          <t>-0.43504505</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.2646331</t>
+          <t>-1.4183146</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.000</t>
+          <t>-0.0996</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8073.20</t>
+          <t xml:space="preserve">   857.29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9067.80</t>
+          <t xml:space="preserve">  2219.10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10185.0</t>
+          <t xml:space="preserve">   5744.30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8087.0</t>
+          <t xml:space="preserve">  6479.0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.001708267</t>
+          <t xml:space="preserve"> 0.86768163</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-0.1212809</t>
+          <t xml:space="preserve"> 0.657487921</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-0.2594223</t>
+          <t xml:space="preserve"> 0.1133920</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>30.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Neocortex grey</t>
+          <t>Mesencephalon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1144,94 +1144,94 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>323010.00</t>
+          <t xml:space="preserve">  4757.70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>411870.0</t>
+          <t xml:space="preserve">  5350.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>525170.0</t>
+          <t xml:space="preserve">   6018.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>584710.0</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.4475645369</t>
+          <t xml:space="preserve"> 0.41169014</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.2955982</t>
+          <t xml:space="preserve"> 0.33834046</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1018283</t>
+          <t xml:space="preserve"> 0.2558456</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.497</t>
+          <t xml:space="preserve"> 1.0000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>330740.00</t>
+          <t xml:space="preserve">  4733.50</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>472550.00</t>
+          <t xml:space="preserve">  5314.90</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>675160.0</t>
+          <t xml:space="preserve">   5967.90</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>584710.0</t>
+          <t xml:space="preserve">  8087.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.434343573</t>
+          <t xml:space="preserve"> 0.41468363</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.1918125</t>
+          <t xml:space="preserve"> 0.342778738</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.1547062</t>
+          <t xml:space="preserve"> 0.2620405</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>25.3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Neocortex white</t>
+          <t>Neocortex grey</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1241,94 +1241,94 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>409800.00</t>
+          <t>541780.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>542610.0</t>
+          <t>668170.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>718450.0</t>
+          <t xml:space="preserve"> 824050.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>421820.0</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.0284851483</t>
+          <t xml:space="preserve"> 0.07341585</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.2863547</t>
+          <t>-0.14274601</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.7032251</t>
+          <t>-0.4093360</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.652</t>
+          <t xml:space="preserve"> 0.5910</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>386360.00</t>
+          <t>672350.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>581630.00</t>
+          <t>918910.00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>875590.0</t>
+          <t>1255900.00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>421820.0</t>
+          <t>584710.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.084069201</t>
+          <t>-0.14989128</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-0.3788544</t>
+          <t>-0.571571058</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-1.0757457</t>
+          <t>-1.1478862</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>33.5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nucleus dentatus cerebelli</t>
+          <t>Neocortex white</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1338,94 +1338,94 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1232.30</t>
+          <t>702360.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1504.5</t>
+          <t>883370.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1836.7</t>
+          <t>1111000.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1166.9</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.0560873352</t>
+          <t>-0.66508386</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.2893004</t>
+          <t>-1.09419663</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.5740133</t>
+          <t>-1.6338971</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.894</t>
+          <t xml:space="preserve"> 1.0700</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1252.00</t>
+          <t>718050.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1588.80</t>
+          <t>819010.00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2016.2</t>
+          <t xml:space="preserve"> 934170.00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1166.9</t>
+          <t>421820.0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-0.072892478</t>
+          <t>-0.70226622</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-0.3615290</t>
+          <t>-0.941615765</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-0.7278165</t>
+          <t>-1.2146194</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>12.3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nucleus subthalamicus Luysi</t>
+          <t>Nucleus dentatus cerebelli</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1435,94 +1435,94 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   792.82</t>
+          <t xml:space="preserve">   498.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008.7</t>
+          <t xml:space="preserve">   602.93</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1283.3</t>
+          <t xml:space="preserve">    729.68</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469.0</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.6904534560</t>
+          <t xml:space="preserve"> 0.57306277</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.1507282</t>
+          <t xml:space="preserve"> 0.48330665</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.7363260</t>
+          <t xml:space="preserve"> 0.3746809</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.100</t>
+          <t xml:space="preserve"> 0.9470</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   336.26</t>
+          <t xml:space="preserve">   555.80</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   705.31</t>
+          <t xml:space="preserve">   688.06</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1479.4</t>
+          <t xml:space="preserve">    851.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   469.0</t>
+          <t xml:space="preserve">  1166.9</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.283019487</t>
+          <t xml:space="preserve"> 0.52369514</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-0.5038587</t>
+          <t xml:space="preserve"> 0.410352865</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-2.1543271</t>
+          <t xml:space="preserve"> 0.2700395</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pallidum</t>
+          <t>Nucleus subthalamicus Luysi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1532,182 +1532,279 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15683.00</t>
+          <t xml:space="preserve">   512.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 19334.0</t>
+          <t xml:space="preserve">   649.73</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23835.0</t>
+          <t xml:space="preserve">    824.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711.0</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.3290429385</t>
+          <t>-0.09207099</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.1040517</t>
+          <t>-0.38535844</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.0594843</t>
+          <t>-0.7574114</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.060</t>
+          <t xml:space="preserve"> 1.1100</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15859.00</t>
+          <t xml:space="preserve">   390.18</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18304.00</t>
+          <t xml:space="preserve">   826.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 21125.0</t>
+          <t xml:space="preserve">   1748.70</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4711.0</t>
+          <t xml:space="preserve">   469.0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-2.366453984</t>
+          <t xml:space="preserve"> 0.16806569</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-2.8853119</t>
+          <t>-0.761239458</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-3.4841392</t>
+          <t>-2.7286170</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>25.2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Pallidum</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7687.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9422.20</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11548.00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4711.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-0.63181293</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-1.00003442</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.4513457</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1.0500</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8058.40</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9462.60</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11111.00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4711.0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-0.71055282</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>-1.008609255</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-1.3586007</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Striatum</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 39986.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 47086.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 55446.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 14860.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17710.00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  21107.00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 28689.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-0.3937613163</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-0.6412446</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.9326724</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0.872</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 44604.00</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 54374.00</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 66284.0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.48202309</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.38267503</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.2642720</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.7500</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 23015.00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 28816.00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  36078.00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve"> 28689.0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-0.554741390</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-0.8952951</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-1.3104445</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.19778175</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>-0.004413484</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-0.2575710</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
